--- a/lessons/chess/excels/remarks_required.xlsx
+++ b/lessons/chess/excels/remarks_required.xlsx
@@ -157,7 +157,7 @@
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+        <t>-border (12:35:31.651) ~0.67, -document (12:37:53.239) ~0.75, -border (12:45:17.066) ~0.67, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -177,7 +177,7 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.82, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.93, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -207,7 +207,7 @@
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>-" (12:35:32.153), -selectedPiece (12:52:27.102), -selectedPiece (12:53:29.626), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +selectdPiece (00:00:00), +selectedPeiece (00:00:00), +null (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +cell (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+        <t>-" (12:35:32.153), -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:53:29.626) ~0.93, -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +selectdPiece (00:00:00), +selectedPeiece (00:00:00), +null (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +cell (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -232,7 +232,7 @@
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>-border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
+        <t>-border (12:35:31.651) ~0.83, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -307,7 +307,7 @@
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -length (12:53:25.380), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
+        <t>-selectedPiece (12:51:24.571) ~0.85, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -length (12:53:25.380) ~0.67, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -322,7 +322,7 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-display (12:04:30.837), +dispaly (00:00:00)</t>
+        <t>-display (12:04:30.837) ~0.71, +dispaly (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -342,7 +342,7 @@
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-cells (12:38:41.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +element (00:00:00)</t>
+        <t>-cells (12:38:41.433) ~0.14, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +element (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -357,17 +357,17 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406), +chess (00:00:00), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406) ~0.00, +chess (00:00:00), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00)</t>
+        <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
+        <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -387,7 +387,7 @@
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
       <text>
-        <t>-cells (12:45:13.133), +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
+        <t>-cells (12:45:13.133) ~0.80, +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H46" authorId="0" shapeId="0">
@@ -432,7 +432,7 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+        <t>-dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
@@ -447,7 +447,7 @@
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), ( (x2), ) (x2), . (x2), 4px, ;, =, border, cell, cells, const, element (x2), for, function, getElementaryByClassName, handleClick, htm, of, red, selectededPiece, solid, style, { (x2), (*, )*, .*, ;*, console*, element*, log*</t>
+        <t>" (x2), ( (x2), ) (x2), . (x2), 4px, ;, =, border, cell, cells, const, element (x2), for, function, getElementaryByClassName, handleClick, of, red, selectededPiece, solid, style, { (x2)</t>
       </text>
     </comment>
     <comment ref="H50" authorId="0" shapeId="0">
@@ -457,17 +457,17 @@
     </comment>
     <comment ref="J50" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), += (00:00:00), +border (00:00:00), +cell (00:00:00), +cells (00:00:00), +const (00:00:00), +element (00:00:00), +element (00:00:00), +for (00:00:00), +function (00:00:00), +getElementaryByClassName (00:00:00), +handleClick (00:00:00), +htm (00:00:00), +of (00:00:00), +red (00:00:00), +selectededPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +{ (00:00:00), +{ (00:00:00), -html (11:53:51.658), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +console* (12:35:18.184), +.* (12:35:18.185), +log* (12:35:18.188), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
+        <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), += (00:00:00), +border (00:00:00), +cell (00:00:00), +cells (00:00:00), +const (00:00:00), +element (00:00:00), +element (00:00:00), +for (00:00:00), +function (00:00:00), +getElementaryByClassName (00:00:00), +handleClick (00:00:00), +of (00:00:00), +red (00:00:00), +selectededPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +{ (00:00:00), +{ (00:00:00), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
       </text>
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (11:53:51.658), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +htm (00:00:00)</t>
+        <t>-&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>+console* (12:35:18.184), +.* (12:35:18.185), +log* (12:35:18.188), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+        <t>-getElementsByClassName (12:37:56.278) ~0.88, -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626) ~0.87, -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -512,17 +512,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-img (12:17:42.332), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +handleclick (00:00:00), +long (00:00:00)</t>
+        <t>-img (12:17:42.332) ~0.67, +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +handleclick (00:00:00), +long (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>+console* (12:35:18.184), +.* (12:35:18.185), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -handleClick (12:41:05.134), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102)</t>
+        <t>+console* (12:35:18.184), +.* (12:35:18.185), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -handleClick (12:41:05.134) ~0.91, -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -547,7 +547,7 @@
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
       <text>
-        <t>-function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:52:11.048), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
+        <t>-function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:52:11.048) ~0.92, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -567,7 +567,7 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-dark (11:58:37.525), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +black (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
+        <t>-dark (11:58:37.525) ~0.40, -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +black (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
@@ -577,7 +577,7 @@
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00)</t>
+        <t>-cells (12:37:50.791) ~0.00, -getElementsByClassName (12:37:56.278) ~0.55, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048) ~0.85, -replaceChildren (12:52:19.891) ~0.80, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.85, -selectedPiece (12:53:29.626) ~0.92, -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -592,22 +592,22 @@
     </comment>
     <comment ref="J70" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +: (00:00:00), +: (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +cell (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +coloumns (00:00:00), +dark (00:00:00), +dark (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +fraction (00:00:00), +getElement (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00), +sBYClassName (00:00:00), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -center (12:24:03.906), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102)</t>
+        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +: (00:00:00), +: (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +cell (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +coloumns (00:00:00), +dark (00:00:00), +dark (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +fraction (00:00:00), +getElement (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00), +sBYClassName (00:00:00), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -center (12:24:03.906), -; (12:24:04.138), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102)</t>
       </text>
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406) ~0.00, +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -center (12:24:03.906), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00)</t>
+        <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00)</t>
+        <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120) ~0.86, -replaceChildren (12:52:19.891) ~0.94, +const* (12:56:52.436), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -657,7 +657,7 @@
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-children (12:53:24.251), -} (12:53:34.736)</t>
+        <t>-children (12:53:24.251) ~0.88, -} (12:53:34.736)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -677,7 +677,7 @@
     </comment>
     <comment ref="Q73" authorId="0" shapeId="0">
       <text>
-        <t>-element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
+        <t>-element (12:33:31.280) ~0.88, -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134) ~0.82, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D75" authorId="0" shapeId="0">
@@ -712,7 +712,7 @@
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -. (12:45:15.654), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00)</t>
+        <t>-getElementsByClassName (12:37:56.278) ~0.95, -handleClick (12:41:05.134) ~0.91, -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -. (12:45:15.654), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -727,7 +727,7 @@
     </comment>
     <comment ref="Q78" authorId="0" shapeId="0">
       <text>
-        <t>-replaceChildren (12:52:19.891), +replacechildren (00:00:00)</t>
+        <t>-replaceChildren (12:52:19.891) ~0.93, +replacechildren (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -735,26 +735,11 @@
         <t>-* (12:05:03.545), -1 (12:05:04.012), -fraction (12:05:06.056), -* (12:05:06.883), -/ (12:43:01.602), -/ (12:43:01.759)</t>
       </text>
     </comment>
-    <comment ref="E82" authorId="0" shapeId="0">
-      <text>
-        <t>" (x2)</t>
-      </text>
-    </comment>
     <comment ref="H82" authorId="0" shapeId="0">
       <text>
         <t>+! (00:00:00), +! (00:00:00), +! (00:00:00), +! (00:00:00), +! (00:00:00), +! (00:00:00), +! (00:00:00), +! (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +4 (00:00:00), +5 (00:00:00), +6 (00:00:00), +7 (00:00:00), +8 (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00), +Row (00:00:00)</t>
       </text>
     </comment>
-    <comment ref="J82" authorId="0" shapeId="0">
-      <text>
-        <t>+" (00:00:00), +" (00:00:00)</t>
-      </text>
-    </comment>
-    <comment ref="Q82" authorId="0" shapeId="0">
-      <text>
-        <t>+" (00:00:00), +" (00:00:00)</t>
-      </text>
-    </comment>
     <comment ref="E83" authorId="0" shapeId="0">
       <text>
         <t>handelClick, const*</t>
@@ -772,7 +757,7 @@
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-handleClick (12:33:15.189), +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
+        <t>-handleClick (12:33:15.189) ~0.82, +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1339,7 +1324,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+          <t>-border (12:35:31.651) ~0.67, -document (12:37:53.239) ~0.75, -border (12:45:17.066) ~0.67, -selectedPiece (12:51:24.571) ~0.92, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.92, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1409,7 +1394,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.82, -handleClick (12:41:05.134) ~0.91, -selectedPiece (12:51:24.571) ~0.93, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1595,7 +1580,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-" (12:35:32.153), -selectedPiece (12:52:27.102), -selectedPiece (12:53:29.626), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +selectdPiece (00:00:00), +selectedPeiece (00:00:00), +null (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +cell (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+          <t>-" (12:35:32.153), -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:53:29.626) ~0.93, -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +selectdPiece (00:00:00), +selectedPeiece (00:00:00), +null (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +cell (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2021,7 +2006,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
+          <t>-border (12:35:31.651) ~0.83, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2369,7 +2354,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -length (12:53:25.380), -selectedPiece (12:53:29.626), +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
+          <t>-selectedPiece (12:51:24.571) ~0.85, -selectedPiece (12:52:11.048) ~0.92, -replaceChildren (12:52:19.891) ~0.93, -selectedPiece (12:52:27.102) ~0.92, -selectedPiece (12:52:30.641) ~0.92, -length (12:53:25.380) ~0.67, -selectedPiece (12:53:29.626) ~0.92, +const* (12:56:52.436), -let (12:56:53.102), +selectedpice (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2577,7 +2562,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-display (12:04:30.837), +dispaly (00:00:00)</t>
+          <t>-display (12:04:30.837) ~0.71, +dispaly (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2655,7 +2640,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-cells (12:38:41.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +element (00:00:00)</t>
+          <t>-cells (12:38:41.433) ~0.14, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +element (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2865,7 +2850,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406), +chess (00:00:00), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406) ~0.00, +chess (00:00:00), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2873,7 +2858,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00)</t>
+          <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +coloumns (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -2881,7 +2866,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
+          <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120) ~0.86, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3243,7 +3228,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>-cells (12:45:13.133), +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
+          <t>-cells (12:45:13.133) ~0.80, +const* (12:56:52.436), -let (12:56:53.102), +cell (00:00:00)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -3411,7 +3396,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+          <t>-dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3491,11 +3476,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>" (x2), ( (x2), ) (x2), . (x2), 4px, ;, =, border, cell, cells, const, element (x2), for, function, getElementaryByClassName, handleClick, htm, of, red, selectededPiece, solid, style, { (x2), (*, )*, .*, ;*, console*, element*, log*</t>
+          <t>" (x2), ( (x2), ) (x2), . (x2), 4px, ;, =, border, cell, cells, const, element (x2), for, function, getElementaryByClassName, handleClick, of, red, selectededPiece, solid, style, { (x2)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3510,20 +3495,20 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>67.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), += (00:00:00), +border (00:00:00), +cell (00:00:00), +cells (00:00:00), +const (00:00:00), +element (00:00:00), +element (00:00:00), +for (00:00:00), +function (00:00:00), +getElementaryByClassName (00:00:00), +handleClick (00:00:00), +htm (00:00:00), +of (00:00:00), +red (00:00:00), +selectededPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +{ (00:00:00), +{ (00:00:00), -html (11:53:51.658), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +console* (12:35:18.184), +.* (12:35:18.185), +log* (12:35:18.188), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
+          <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), += (00:00:00), +border (00:00:00), +cell (00:00:00), +cells (00:00:00), +const (00:00:00), +element (00:00:00), +element (00:00:00), +for (00:00:00), +function (00:00:00), +getElementaryByClassName (00:00:00), +handleClick (00:00:00), +of (00:00:00), +red (00:00:00), +selectededPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +{ (00:00:00), +{ (00:00:00), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (11:53:51.658), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), +htm (00:00:00)</t>
+          <t>-&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3531,11 +3516,11 @@
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>49.6</v>
+        <v>55.1</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>+console* (12:35:18.184), +.* (12:35:18.185), +log* (12:35:18.188), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+          <t>-getElementsByClassName (12:37:56.278) ~0.88, -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626) ~0.87, -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3957,7 +3942,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-img (12:17:42.332), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +handleclick (00:00:00), +long (00:00:00)</t>
+          <t>-img (12:17:42.332) ~0.67, +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +handleclick (00:00:00), +long (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -3965,7 +3950,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>+console* (12:35:18.184), +.* (12:35:18.185), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -handleClick (12:41:05.134), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102)</t>
+          <t>+console* (12:35:18.184), +.* (12:35:18.185), +(* (12:35:18.189), +element* (12:35:18.196), +)* (12:35:18.197), +;* (12:35:18.198), -handleClick (12:41:05.134) ~0.91, -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4281,7 +4266,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>-function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:52:11.048), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
+          <t>-function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:52:11.048) ~0.92, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -4381,7 +4366,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-dark (11:58:37.525), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +black (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
+          <t>-dark (11:58:37.525) ~0.40, -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +black (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4397,7 +4382,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00)</t>
+          <t>-cells (12:37:50.791) ~0.00, -getElementsByClassName (12:37:56.278) ~0.55, -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048) ~0.85, -replaceChildren (12:52:19.891) ~0.80, -selectedPiece (12:52:27.102) ~0.85, -selectedPiece (12:52:30.641) ~0.85, -selectedPiece (12:53:29.626) ~0.92, -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4484,11 +4469,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +: (00:00:00), +: (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +cell (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +coloumns (00:00:00), +dark (00:00:00), +dark (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +fraction (00:00:00), +getElement (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00), +sBYClassName (00:00:00), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -center (12:24:03.906), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102)</t>
+          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +: (00:00:00), +: (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +cell (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +coloumns (00:00:00), +dark (00:00:00), +dark (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +fraction (00:00:00), +getElement (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00), +sBYClassName (00:00:00), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -center (12:24:03.906), -; (12:24:04.138), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4497,15 +4482,15 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406), +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -" (12:26:40.406) ~0.00, +' (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +dark (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>80.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -center (12:24:03.906), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00)</t>
+          <t>-; (12:02:47.484) ~0.00, -; (12:02:56.888) ~0.00, -columns (12:05:17.007) ~0.88, -center (12:24:03.906), -; (12:24:04.138), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), +: (00:00:00), +: (00:00:00), +/ (00:00:00), +1 (00:00:00), +fraction (00:00:00), +/ (00:00:00), +coloumns (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4513,7 +4498,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -replaceChildren (12:52:19.891), +const* (12:56:52.436), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00)</t>
+          <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120) ~0.86, -replaceChildren (12:52:19.891) ~0.94, +const* (12:56:52.436), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +replaceChirldren (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4661,7 +4646,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-children (12:53:24.251), -} (12:53:34.736)</t>
+          <t>-children (12:53:24.251) ~0.88, -} (12:53:34.736)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4731,7 +4716,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>-element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
+          <t>-element (12:33:31.280) ~0.88, -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134) ~0.82, -} (12:53:34.736), +const* (12:56:52.436), -let (12:56:53.102), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -4847,7 +4832,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -. (12:45:15.654), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00)</t>
+          <t>-getElementsByClassName (12:37:56.278) ~0.95, -handleClick (12:41:05.134) ~0.91, -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -. (12:45:15.654), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -} (12:53:34.736), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -4989,7 +4974,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>-replaceChildren (12:52:19.891), +replacechildren (00:00:00)</t>
+          <t>-replaceChildren (12:52:19.891) ~0.93, +replacechildren (00:00:00)</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -5173,13 +5158,9 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>" (x2)</t>
-        </is>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -5192,13 +5173,9 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>+" (00:00:00), +" (00:00:00)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>100</v>
@@ -5209,13 +5186,9 @@
       </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>+" (00:00:00), +" (00:00:00)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>_</t>
@@ -5283,7 +5256,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-handleClick (12:33:15.189), +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
+          <t>-handleClick (12:33:15.189) ~0.82, +const* (12:56:52.436), -let (12:56:53.102), +handelClick (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
